--- a/src/main/File/TestData.xlsx
+++ b/src/main/File/TestData.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rafi\Desktop\New folder\ReadDataFromXL\src\main\File\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE6F971-40F6-4FE8-8DD7-F317271EBACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A1AAC742-A888-4FAC-9C19-9A2A9C2E49AE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,42 +24,57 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
-  <si>
-    <t>David</t>
-  </si>
-  <si>
-    <t>Miller</t>
-  </si>
-  <si>
-    <t xml:space="preserve">John </t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Cena</t>
   </si>
   <si>
-    <t>Warner</t>
-  </si>
-  <si>
-    <t>MITCHEL</t>
-  </si>
-  <si>
-    <t>Starc</t>
-  </si>
-  <si>
-    <t>1111</t>
-  </si>
-  <si>
     <t>1212</t>
   </si>
   <si>
     <t>1112</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>Postcode</t>
+  </si>
+  <si>
+    <t>1213</t>
+  </si>
+  <si>
+    <t>MS</t>
+  </si>
+  <si>
+    <t>Dhoni</t>
+  </si>
+  <si>
+    <t>Leo</t>
+  </si>
+  <si>
+    <t>Messi</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Smiri</t>
+  </si>
+  <si>
+    <t>Mandhana</t>
+  </si>
+  <si>
+    <t>1314</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -406,55 +420,68 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C29DA204-D457-48C5-A34C-5F86897D04A0}">
-  <dimension ref="A1:C4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
     <col min="3" max="3" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>9</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
